--- a/data/nzd0587/nzd0587.xlsx
+++ b/data/nzd0587/nzd0587.xlsx
@@ -14900,9 +14900,15 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+      <c r="F2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.1393</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
@@ -14950,9 +14956,15 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+      <c r="F3" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.0472</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.1105</v>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
@@ -15000,9 +15012,15 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="F4" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.08160000000000001</v>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
@@ -15050,9 +15068,15 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="F5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.0892</v>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
@@ -15100,9 +15124,15 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.121</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>

--- a/data/nzd0587/nzd0587.xlsx
+++ b/data/nzd0587/nzd0587.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G458"/>
+  <dimension ref="A1:G459"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12794,6 +12794,33 @@
       <c r="G458" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-13 22:27:38+00:00</t>
+        </is>
+      </c>
+      <c r="B459" t="n">
+        <v>220.26</v>
+      </c>
+      <c r="C459" t="n">
+        <v>178.18</v>
+      </c>
+      <c r="D459" t="n">
+        <v>185.14</v>
+      </c>
+      <c r="E459" t="n">
+        <v>171.57</v>
+      </c>
+      <c r="F459" t="n">
+        <v>241.72</v>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -12808,7 +12835,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B529"/>
+  <dimension ref="A1:B530"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18101,6 +18128,16 @@
       </c>
       <c r="B529" t="n">
         <v>0.33</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>2025-12-13 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B530" t="n">
+        <v>0.57</v>
       </c>
     </row>
   </sheetData>
@@ -18263,28 +18300,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.02805584232924522</v>
+        <v>-0.02838789687703222</v>
       </c>
       <c r="J2" t="n">
+        <v>458</v>
+      </c>
+      <c r="K2" t="n">
         <v>457</v>
       </c>
-      <c r="K2" t="n">
-        <v>456</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.001483565964824463</v>
+        <v>0.001526030830673153</v>
       </c>
       <c r="M2" t="n">
-        <v>3.606056934686076</v>
+        <v>3.600237940238974</v>
       </c>
       <c r="N2" t="n">
-        <v>31.53147789226257</v>
+        <v>31.463855624018</v>
       </c>
       <c r="O2" t="n">
-        <v>5.615289653460681</v>
+        <v>5.609265159004163</v>
       </c>
       <c r="P2" t="n">
-        <v>221.7940837302873</v>
+        <v>221.7973329576074</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18335,28 +18372,28 @@
         <v>0.1105</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.465303927868762</v>
+        <v>-0.4649179012986487</v>
       </c>
       <c r="J3" t="n">
+        <v>458</v>
+      </c>
+      <c r="K3" t="n">
         <v>457</v>
       </c>
-      <c r="K3" t="n">
-        <v>456</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.3068578856611847</v>
+        <v>0.3075107010422662</v>
       </c>
       <c r="M3" t="n">
-        <v>3.821949001092995</v>
+        <v>3.815566787687537</v>
       </c>
       <c r="N3" t="n">
-        <v>28.87090146192206</v>
+        <v>28.80956311552071</v>
       </c>
       <c r="O3" t="n">
-        <v>5.373164939020769</v>
+        <v>5.367454062730366</v>
       </c>
       <c r="P3" t="n">
-        <v>189.5549200514319</v>
+        <v>189.551120380335</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18407,28 +18444,28 @@
         <v>0.08160000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.05217014358962341</v>
+        <v>0.05187318709095189</v>
       </c>
       <c r="J4" t="n">
+        <v>458</v>
+      </c>
+      <c r="K4" t="n">
         <v>457</v>
       </c>
-      <c r="K4" t="n">
-        <v>456</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.002669749468656502</v>
+        <v>0.002652118078925736</v>
       </c>
       <c r="M4" t="n">
-        <v>6.326185274556567</v>
+        <v>6.314174572155564</v>
       </c>
       <c r="N4" t="n">
-        <v>60.02255193730575</v>
+        <v>59.89229833816438</v>
       </c>
       <c r="O4" t="n">
-        <v>7.747422276945136</v>
+        <v>7.739011457425579</v>
       </c>
       <c r="P4" t="n">
-        <v>184.471783222668</v>
+        <v>184.4747061743827</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18479,28 +18516,28 @@
         <v>0.0892</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1881259058749565</v>
+        <v>-0.1912071055526752</v>
       </c>
       <c r="J5" t="n">
+        <v>458</v>
+      </c>
+      <c r="K5" t="n">
         <v>457</v>
       </c>
-      <c r="K5" t="n">
-        <v>456</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.01677578899000898</v>
+        <v>0.01738559031425335</v>
       </c>
       <c r="M5" t="n">
-        <v>9.029764148996819</v>
+        <v>9.027369591489313</v>
       </c>
       <c r="N5" t="n">
-        <v>122.452801751729</v>
+        <v>122.3018548393115</v>
       </c>
       <c r="O5" t="n">
-        <v>11.06583940565418</v>
+        <v>11.05901690202667</v>
       </c>
       <c r="P5" t="n">
-        <v>183.8766836266091</v>
+        <v>183.907011967365</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -18551,28 +18588,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1180342673992495</v>
+        <v>-0.1165871764528991</v>
       </c>
       <c r="J6" t="n">
+        <v>458</v>
+      </c>
+      <c r="K6" t="n">
         <v>457</v>
       </c>
-      <c r="K6" t="n">
-        <v>456</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.02317178611724047</v>
+        <v>0.02270948330575329</v>
       </c>
       <c r="M6" t="n">
-        <v>4.610201767876042</v>
+        <v>4.607019195582065</v>
       </c>
       <c r="N6" t="n">
-        <v>34.67183363552216</v>
+        <v>34.62177282167478</v>
       </c>
       <c r="O6" t="n">
-        <v>5.888279344216114</v>
+        <v>5.88402692224252</v>
       </c>
       <c r="P6" t="n">
-        <v>241.3925217675568</v>
+        <v>241.3782780080098</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -18610,7 +18647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G458"/>
+  <dimension ref="A1:G459"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35539,6 +35576,43 @@
         </is>
       </c>
     </row>
+    <row r="459">
+      <c r="A459" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-13 22:27:38+00:00</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>-46.88973544281497,168.13915766980213</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>-46.88894506878949,168.13888577737458</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>-46.88883357762986,168.13774726423975</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>-46.88893464091112,168.1366942985562</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>-46.88975261033649,168.13597305090374</t>
+        </is>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0587/nzd0587.xlsx
+++ b/data/nzd0587/nzd0587.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G459"/>
+  <dimension ref="A1:G461"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12821,6 +12821,60 @@
       <c r="G459" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-07 22:27:36+00:00</t>
+        </is>
+      </c>
+      <c r="B460" t="n">
+        <v>219.77</v>
+      </c>
+      <c r="C460" t="n">
+        <v>179.14</v>
+      </c>
+      <c r="D460" t="n">
+        <v>186.82</v>
+      </c>
+      <c r="E460" t="n">
+        <v>188.75</v>
+      </c>
+      <c r="F460" t="n">
+        <v>238.17</v>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-23 22:27:30+00:00</t>
+        </is>
+      </c>
+      <c r="B461" t="n">
+        <v>219.2</v>
+      </c>
+      <c r="C461" t="n">
+        <v>179.22</v>
+      </c>
+      <c r="D461" t="n">
+        <v>187.14</v>
+      </c>
+      <c r="E461" t="n">
+        <v>190.73</v>
+      </c>
+      <c r="F461" t="n">
+        <v>237.57</v>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -12835,7 +12889,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B530"/>
+  <dimension ref="A1:B532"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18138,6 +18192,26 @@
       </c>
       <c r="B530" t="n">
         <v>0.57</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>2026-02-07 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B531" t="n">
+        <v>-0.38</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>2026-02-23 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B532" t="n">
+        <v>-0.25</v>
       </c>
     </row>
   </sheetData>
@@ -18300,28 +18374,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.02838789687703222</v>
+        <v>-0.02969124363214617</v>
       </c>
       <c r="J2" t="n">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="K2" t="n">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001526030830673153</v>
+        <v>0.001684819537043247</v>
       </c>
       <c r="M2" t="n">
-        <v>3.600237940238974</v>
+        <v>3.592530217667253</v>
       </c>
       <c r="N2" t="n">
-        <v>31.463855624018</v>
+        <v>31.33753463495683</v>
       </c>
       <c r="O2" t="n">
-        <v>5.609265159004163</v>
+        <v>5.597993804476459</v>
       </c>
       <c r="P2" t="n">
-        <v>221.7973329576074</v>
+        <v>221.810192343273</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18372,28 +18446,28 @@
         <v>0.1105</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4649179012986487</v>
+        <v>-0.4632442278246497</v>
       </c>
       <c r="J3" t="n">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="K3" t="n">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3075107010422662</v>
+        <v>0.3079235465409289</v>
       </c>
       <c r="M3" t="n">
-        <v>3.815566787687537</v>
+        <v>3.807368847534607</v>
       </c>
       <c r="N3" t="n">
-        <v>28.80956311552071</v>
+        <v>28.70106454199968</v>
       </c>
       <c r="O3" t="n">
-        <v>5.367454062730366</v>
+        <v>5.357337448957241</v>
       </c>
       <c r="P3" t="n">
-        <v>189.551120380335</v>
+        <v>189.5345134125182</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18444,28 +18518,28 @@
         <v>0.08160000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.05187318709095189</v>
+        <v>0.0528203430177259</v>
       </c>
       <c r="J4" t="n">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="K4" t="n">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002652118078925736</v>
+        <v>0.002776175347148802</v>
       </c>
       <c r="M4" t="n">
-        <v>6.314174572155564</v>
+        <v>6.290604288276611</v>
       </c>
       <c r="N4" t="n">
-        <v>59.89229833816438</v>
+        <v>59.63688975942168</v>
       </c>
       <c r="O4" t="n">
-        <v>7.739011457425579</v>
+        <v>7.722492457712191</v>
       </c>
       <c r="P4" t="n">
-        <v>184.4747061743827</v>
+        <v>184.4653069723658</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18516,28 +18590,28 @@
         <v>0.0892</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1912071055526752</v>
+        <v>-0.1820271912350508</v>
       </c>
       <c r="J5" t="n">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="K5" t="n">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01738559031425335</v>
+        <v>0.01586788228234826</v>
       </c>
       <c r="M5" t="n">
-        <v>9.027369591489313</v>
+        <v>9.031263258874336</v>
       </c>
       <c r="N5" t="n">
-        <v>122.3018548393115</v>
+        <v>122.2851638826085</v>
       </c>
       <c r="O5" t="n">
-        <v>11.05901690202667</v>
+        <v>11.05826224515446</v>
       </c>
       <c r="P5" t="n">
-        <v>183.907011967365</v>
+        <v>183.8159187556431</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -18588,28 +18662,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1165871764528991</v>
+        <v>-0.1169303589843885</v>
       </c>
       <c r="J6" t="n">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="K6" t="n">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02270948330575329</v>
+        <v>0.02305809579138662</v>
       </c>
       <c r="M6" t="n">
-        <v>4.607019195582065</v>
+        <v>4.588845879791248</v>
       </c>
       <c r="N6" t="n">
-        <v>34.62177282167478</v>
+        <v>34.47201452484926</v>
       </c>
       <c r="O6" t="n">
-        <v>5.88402692224252</v>
+        <v>5.871287297079683</v>
       </c>
       <c r="P6" t="n">
-        <v>241.3782780080098</v>
+        <v>241.3816856066641</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -18647,7 +18721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G459"/>
+  <dimension ref="A1:G461"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35613,6 +35687,80 @@
         </is>
       </c>
     </row>
+    <row r="460">
+      <c r="A460" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-07 22:27:36+00:00</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>-46.88973255402489,168.13916251491608</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>-46.888950728441195,168.13887628502454</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>-46.888847965975145,168.13775391136548</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>-46.88908177938058,168.13676227065253</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>-46.88972221539087,168.13595896348795</t>
+        </is>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-23 22:27:30+00:00</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>-46.88972919359533,168.13916815106836</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>-46.888951200078814,168.13887549399527</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>-46.88885070661231,168.13775517748502</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>-46.889098737130155,168.13677010447856</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>-46.88971707821683,168.1359565825177</t>
+        </is>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0587/nzd0587.xlsx
+++ b/data/nzd0587/nzd0587.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G461"/>
+  <dimension ref="A1:G462"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12875,6 +12875,33 @@
       <c r="G461" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-03 22:27:18+00:00</t>
+        </is>
+      </c>
+      <c r="B462" t="n">
+        <v>218.99</v>
+      </c>
+      <c r="C462" t="n">
+        <v>178.21</v>
+      </c>
+      <c r="D462" t="n">
+        <v>187.16</v>
+      </c>
+      <c r="E462" t="n">
+        <v>190.41</v>
+      </c>
+      <c r="F462" t="n">
+        <v>234.92</v>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -12889,7 +12916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B532"/>
+  <dimension ref="A1:B533"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18212,6 +18239,16 @@
       </c>
       <c r="B532" t="n">
         <v>-0.25</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>2026-03-03 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B533" t="n">
+        <v>-0.46</v>
       </c>
     </row>
   </sheetData>
@@ -18374,28 +18411,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.02969124363214617</v>
+        <v>-0.03053759379528697</v>
       </c>
       <c r="J2" t="n">
+        <v>461</v>
+      </c>
+      <c r="K2" t="n">
         <v>460</v>
       </c>
-      <c r="K2" t="n">
-        <v>459</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.001684819537043247</v>
+        <v>0.001790163741910322</v>
       </c>
       <c r="M2" t="n">
-        <v>3.592530217667253</v>
+        <v>3.589874049472622</v>
       </c>
       <c r="N2" t="n">
-        <v>31.33753463495683</v>
+        <v>31.27831560062398</v>
       </c>
       <c r="O2" t="n">
-        <v>5.597993804476459</v>
+        <v>5.592701994619772</v>
       </c>
       <c r="P2" t="n">
-        <v>221.810192343273</v>
+        <v>221.8185580161527</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18446,28 +18483,28 @@
         <v>0.1105</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4632442278246497</v>
+        <v>-0.4628209973587465</v>
       </c>
       <c r="J3" t="n">
+        <v>461</v>
+      </c>
+      <c r="K3" t="n">
         <v>460</v>
       </c>
-      <c r="K3" t="n">
-        <v>459</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.3079235465409289</v>
+        <v>0.3085498077499722</v>
       </c>
       <c r="M3" t="n">
-        <v>3.807368847534607</v>
+        <v>3.80122228358471</v>
       </c>
       <c r="N3" t="n">
-        <v>28.70106454199968</v>
+        <v>28.6408728307027</v>
       </c>
       <c r="O3" t="n">
-        <v>5.357337448957241</v>
+        <v>5.351716811519712</v>
       </c>
       <c r="P3" t="n">
-        <v>189.5345134125182</v>
+        <v>189.5303056984307</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18518,28 +18555,28 @@
         <v>0.08160000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0528203430177259</v>
+        <v>0.05335800766123165</v>
       </c>
       <c r="J4" t="n">
+        <v>461</v>
+      </c>
+      <c r="K4" t="n">
         <v>460</v>
       </c>
-      <c r="K4" t="n">
-        <v>459</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.002776175347148802</v>
+        <v>0.002846361356458771</v>
       </c>
       <c r="M4" t="n">
-        <v>6.290604288276611</v>
+        <v>6.279153458383015</v>
       </c>
       <c r="N4" t="n">
-        <v>59.63688975942168</v>
+        <v>59.5107979436008</v>
       </c>
       <c r="O4" t="n">
-        <v>7.722492457712191</v>
+        <v>7.714324205243178</v>
       </c>
       <c r="P4" t="n">
-        <v>184.4653069723658</v>
+        <v>184.4599615653663</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18590,28 +18627,28 @@
         <v>0.0892</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1820271912350508</v>
+        <v>-0.1772307915677295</v>
       </c>
       <c r="J5" t="n">
+        <v>461</v>
+      </c>
+      <c r="K5" t="n">
         <v>460</v>
       </c>
-      <c r="K5" t="n">
-        <v>459</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.01586788228234826</v>
+        <v>0.01509260725433959</v>
       </c>
       <c r="M5" t="n">
-        <v>9.031263258874336</v>
+        <v>9.034118357771852</v>
       </c>
       <c r="N5" t="n">
-        <v>122.2851638826085</v>
+        <v>122.3021242934258</v>
       </c>
       <c r="O5" t="n">
-        <v>11.05826224515446</v>
+        <v>11.05902908457274</v>
       </c>
       <c r="P5" t="n">
-        <v>183.8159187556431</v>
+        <v>183.7682334397803</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -18662,28 +18699,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1169303589843885</v>
+        <v>-0.1183319852932794</v>
       </c>
       <c r="J6" t="n">
+        <v>461</v>
+      </c>
+      <c r="K6" t="n">
         <v>460</v>
       </c>
-      <c r="K6" t="n">
-        <v>459</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.02305809579138662</v>
+        <v>0.02369666733090536</v>
       </c>
       <c r="M6" t="n">
-        <v>4.588845879791248</v>
+        <v>4.586599085388711</v>
       </c>
       <c r="N6" t="n">
-        <v>34.47201452484926</v>
+        <v>34.42122494730176</v>
       </c>
       <c r="O6" t="n">
-        <v>5.871287297079683</v>
+        <v>5.866960452167865</v>
       </c>
       <c r="P6" t="n">
-        <v>241.3816856066641</v>
+        <v>241.3956204323452</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -18721,7 +18758,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G461"/>
+  <dimension ref="A1:G462"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35761,6 +35798,43 @@
         </is>
       </c>
     </row>
+    <row r="462">
+      <c r="A462" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-03 22:27:18+00:00</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>-46.88972795554226,168.13917022754538</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>-46.88894524565362,168.13888548073868</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>-46.88885087790214,168.13775525661748</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>-46.88909599648378,168.13676883840535</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>-46.889694389031106,168.1359460665709</t>
+        </is>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0587/nzd0587.xlsx
+++ b/data/nzd0587/nzd0587.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G462"/>
+  <dimension ref="A1:G464"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12900,6 +12900,60 @@
         <v>234.92</v>
       </c>
       <c r="G462" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-19 22:27:09+00:00</t>
+        </is>
+      </c>
+      <c r="B463" t="n">
+        <v>226.38</v>
+      </c>
+      <c r="C463" t="n">
+        <v>178.7</v>
+      </c>
+      <c r="D463" t="n">
+        <v>187.29</v>
+      </c>
+      <c r="E463" t="n">
+        <v>190.88</v>
+      </c>
+      <c r="F463" t="n">
+        <v>232.67</v>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:20:45+00:00</t>
+        </is>
+      </c>
+      <c r="B464" t="n">
+        <v>228.75</v>
+      </c>
+      <c r="C464" t="n">
+        <v>181.11</v>
+      </c>
+      <c r="D464" t="n">
+        <v>187.91</v>
+      </c>
+      <c r="E464" t="n">
+        <v>190.67</v>
+      </c>
+      <c r="F464" t="n">
+        <v>232.09</v>
+      </c>
+      <c r="G464" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -12916,7 +12970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B533"/>
+  <dimension ref="A1:B535"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18249,6 +18303,26 @@
       </c>
       <c r="B533" t="n">
         <v>-0.46</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>2026-03-19 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B534" t="n">
+        <v>-0.52</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B535" t="n">
+        <v>0.64</v>
       </c>
     </row>
   </sheetData>
@@ -18411,28 +18485,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.03053759379528697</v>
+        <v>-0.02510344253733166</v>
       </c>
       <c r="J2" t="n">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="K2" t="n">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001790163741910322</v>
+        <v>0.001214754064737145</v>
       </c>
       <c r="M2" t="n">
-        <v>3.589874049472622</v>
+        <v>3.597658289696921</v>
       </c>
       <c r="N2" t="n">
-        <v>31.27831560062398</v>
+        <v>31.33298614968949</v>
       </c>
       <c r="O2" t="n">
-        <v>5.592701994619772</v>
+        <v>5.597587529435292</v>
       </c>
       <c r="P2" t="n">
-        <v>221.8185580161527</v>
+        <v>221.764638816774</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18483,28 +18557,28 @@
         <v>0.1105</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4628209973587465</v>
+        <v>-0.4605412898095697</v>
       </c>
       <c r="J3" t="n">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="K3" t="n">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3085498077499722</v>
+        <v>0.3082213300133869</v>
       </c>
       <c r="M3" t="n">
-        <v>3.80122228358471</v>
+        <v>3.796130428782765</v>
       </c>
       <c r="N3" t="n">
-        <v>28.6408728307027</v>
+        <v>28.55529748546884</v>
       </c>
       <c r="O3" t="n">
-        <v>5.351716811519712</v>
+        <v>5.343715700284666</v>
       </c>
       <c r="P3" t="n">
-        <v>189.5303056984307</v>
+        <v>189.5075457012656</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18555,28 +18629,28 @@
         <v>0.08160000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.05335800766123165</v>
+        <v>0.05478384916002152</v>
       </c>
       <c r="J4" t="n">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="K4" t="n">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002846361356458771</v>
+        <v>0.003028492550689599</v>
       </c>
       <c r="M4" t="n">
-        <v>6.279153458383015</v>
+        <v>6.257796852938236</v>
       </c>
       <c r="N4" t="n">
-        <v>59.5107979436008</v>
+        <v>59.26610539117247</v>
       </c>
       <c r="O4" t="n">
-        <v>7.714324205243178</v>
+        <v>7.698448245664347</v>
       </c>
       <c r="P4" t="n">
-        <v>184.4599615653663</v>
+        <v>184.4457322078026</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18627,28 +18701,28 @@
         <v>0.0892</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1772307915677295</v>
+        <v>-0.1674629584015333</v>
       </c>
       <c r="J5" t="n">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="K5" t="n">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01509260725433959</v>
+        <v>0.01356155308602125</v>
       </c>
       <c r="M5" t="n">
-        <v>9.034118357771852</v>
+        <v>9.040426999624524</v>
       </c>
       <c r="N5" t="n">
-        <v>122.3021242934258</v>
+        <v>122.3610364557037</v>
       </c>
       <c r="O5" t="n">
-        <v>11.05902908457274</v>
+        <v>11.06169229619518</v>
       </c>
       <c r="P5" t="n">
-        <v>183.7682334397803</v>
+        <v>183.6707824232355</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -18699,28 +18773,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1183319852932794</v>
+        <v>-0.1232053758286034</v>
       </c>
       <c r="J6" t="n">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="K6" t="n">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02369666733090536</v>
+        <v>0.02577310119539922</v>
       </c>
       <c r="M6" t="n">
-        <v>4.586599085388711</v>
+        <v>4.593637866542873</v>
       </c>
       <c r="N6" t="n">
-        <v>34.42122494730176</v>
+        <v>34.41896600558194</v>
       </c>
       <c r="O6" t="n">
-        <v>5.866960452167865</v>
+        <v>5.866767935207761</v>
       </c>
       <c r="P6" t="n">
-        <v>241.3956204323452</v>
+        <v>241.4442452145729</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -18758,7 +18832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G462"/>
+  <dimension ref="A1:G464"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35835,6 +35909,80 @@
         </is>
       </c>
     </row>
+    <row r="463">
+      <c r="A463" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-19 22:27:09+00:00</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>-46.88977152319442,168.139097155274</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>-46.88894813443428,168.1388806356852</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>-46.88885199128598,168.1377557709786</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>-46.88910002180812,168.13677069795042</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>-46.889675124627594,168.13593713794327</t>
+        </is>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:20:45+00:00</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>-46.88978549548875,168.1390737207046</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>-46.88896234251543,168.13885680592492</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>-46.88885730127045,168.1377582240857</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>-46.88909822325895,168.1367698670898</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>-46.889670158692375,168.13593483634244</t>
+        </is>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0587/nzd0587.xlsx
+++ b/data/nzd0587/nzd0587.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G464"/>
+  <dimension ref="A1:G467"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12954,6 +12954,87 @@
         <v>232.09</v>
       </c>
       <c r="G464" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:41+00:00</t>
+        </is>
+      </c>
+      <c r="B465" t="n">
+        <v>227.28</v>
+      </c>
+      <c r="C465" t="n">
+        <v>181.25</v>
+      </c>
+      <c r="D465" t="n">
+        <v>188.11</v>
+      </c>
+      <c r="E465" t="n">
+        <v>191.48</v>
+      </c>
+      <c r="F465" t="n">
+        <v>232.66</v>
+      </c>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-14 22:26:49+00:00</t>
+        </is>
+      </c>
+      <c r="B466" t="n">
+        <v>227.38</v>
+      </c>
+      <c r="C466" t="n">
+        <v>181.82</v>
+      </c>
+      <c r="D466" t="n">
+        <v>190.17</v>
+      </c>
+      <c r="E466" t="n">
+        <v>190.83</v>
+      </c>
+      <c r="F466" t="n">
+        <v>234.89</v>
+      </c>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:20:18+00:00</t>
+        </is>
+      </c>
+      <c r="B467" t="n">
+        <v>227.38</v>
+      </c>
+      <c r="C467" t="n">
+        <v>181.27</v>
+      </c>
+      <c r="D467" t="n">
+        <v>189.96</v>
+      </c>
+      <c r="E467" t="n">
+        <v>187.22</v>
+      </c>
+      <c r="F467" t="n">
+        <v>236.56</v>
+      </c>
+      <c r="G467" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -12970,7 +13051,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B535"/>
+  <dimension ref="A1:B538"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18323,6 +18404,36 @@
       </c>
       <c r="B535" t="n">
         <v>0.64</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B536" t="n">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>2026-05-14 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B537" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B538" t="n">
+        <v>0.26</v>
       </c>
     </row>
   </sheetData>
@@ -18485,28 +18596,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.02510344253733166</v>
+        <v>-0.01743255974319417</v>
       </c>
       <c r="J2" t="n">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="K2" t="n">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001214754064737145</v>
+        <v>0.0005899832978841779</v>
       </c>
       <c r="M2" t="n">
-        <v>3.597658289696921</v>
+        <v>3.607933354421723</v>
       </c>
       <c r="N2" t="n">
-        <v>31.33298614968949</v>
+        <v>31.37796613776765</v>
       </c>
       <c r="O2" t="n">
-        <v>5.597587529435292</v>
+        <v>5.601603889759401</v>
       </c>
       <c r="P2" t="n">
-        <v>221.764638816774</v>
+        <v>221.6881812195797</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18557,28 +18668,28 @@
         <v>0.1105</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4605412898095697</v>
+        <v>-0.4552534037357339</v>
       </c>
       <c r="J3" t="n">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="K3" t="n">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3082213300133869</v>
+        <v>0.3055115919997312</v>
       </c>
       <c r="M3" t="n">
-        <v>3.796130428782765</v>
+        <v>3.798806253508947</v>
       </c>
       <c r="N3" t="n">
-        <v>28.55529748546884</v>
+        <v>28.48762973263661</v>
       </c>
       <c r="O3" t="n">
-        <v>5.343715700284666</v>
+        <v>5.337380418579568</v>
       </c>
       <c r="P3" t="n">
-        <v>189.5075457012656</v>
+        <v>189.4545363217463</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18629,28 +18740,28 @@
         <v>0.08160000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.05478384916002152</v>
+        <v>0.0591007161150534</v>
       </c>
       <c r="J4" t="n">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="K4" t="n">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003028492550689599</v>
+        <v>0.003568941998880915</v>
       </c>
       <c r="M4" t="n">
-        <v>6.257796852938236</v>
+        <v>6.234769995170586</v>
       </c>
       <c r="N4" t="n">
-        <v>59.26610539117247</v>
+        <v>58.96656876979839</v>
       </c>
       <c r="O4" t="n">
-        <v>7.698448245664347</v>
+        <v>7.678969251781022</v>
       </c>
       <c r="P4" t="n">
-        <v>184.4457322078026</v>
+        <v>184.4024480061476</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18701,28 +18812,28 @@
         <v>0.0892</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1674629584015333</v>
+        <v>-0.1543098395456054</v>
       </c>
       <c r="J5" t="n">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="K5" t="n">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01356155308602125</v>
+        <v>0.01163442956664573</v>
       </c>
       <c r="M5" t="n">
-        <v>9.040426999624524</v>
+        <v>9.04391541394844</v>
       </c>
       <c r="N5" t="n">
-        <v>122.3610364557037</v>
+        <v>122.312926693738</v>
       </c>
       <c r="O5" t="n">
-        <v>11.06169229619518</v>
+        <v>11.05951747110777</v>
       </c>
       <c r="P5" t="n">
-        <v>183.6707824232355</v>
+        <v>183.5389442057125</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -18773,28 +18884,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1232053758286034</v>
+        <v>-0.1274388683340576</v>
       </c>
       <c r="J6" t="n">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="K6" t="n">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02577310119539922</v>
+        <v>0.02784266432156968</v>
       </c>
       <c r="M6" t="n">
-        <v>4.593637866542873</v>
+        <v>4.588064880896566</v>
       </c>
       <c r="N6" t="n">
-        <v>34.41896600558194</v>
+        <v>34.28800237132437</v>
       </c>
       <c r="O6" t="n">
-        <v>5.866767935207761</v>
+        <v>5.855595816936511</v>
       </c>
       <c r="P6" t="n">
-        <v>241.4442452145729</v>
+        <v>241.4866667976285</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -18832,7 +18943,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G464"/>
+  <dimension ref="A1:G467"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35983,6 +36094,117 @@
         </is>
       </c>
     </row>
+    <row r="465">
+      <c r="A465" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:41+00:00</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>-46.8897768291296,168.13908825607186</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>-46.88896316788099,168.13885542162313</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>-46.88885901416865,168.13775901541064</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>-46.88910516052003,168.1367730718381</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>-46.88967503900803,168.1359370982605</t>
+        </is>
+      </c>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-14 22:26:49+00:00</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>-46.88977741867791,168.1390872672715</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>-46.888966528297644,168.13884978553673</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>-46.88887665701997,168.1377671660605</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>-46.88909959358213,168.13677050012646</t>
+        </is>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>-46.88969413217241,168.13594594752252</t>
+        </is>
+      </c>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:20:18+00:00</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>-46.88977741867791,168.1390872672715</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>-46.88896328579034,168.1388552238657</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>-46.888874858476896,168.13776633516878</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>-46.889068675664745,168.13675621724465</t>
+        </is>
+      </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>-46.889708430640475,168.1359525745521</t>
+        </is>
+      </c>
+      <c r="G467" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0587/nzd0587.xlsx
+++ b/data/nzd0587/nzd0587.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G467"/>
+  <dimension ref="A1:G469"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13037,6 +13037,60 @@
       <c r="G467" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-30 22:26:38+00:00</t>
+        </is>
+      </c>
+      <c r="B468" t="n">
+        <v>228.79</v>
+      </c>
+      <c r="C468" t="n">
+        <v>180.83</v>
+      </c>
+      <c r="D468" t="n">
+        <v>191.87</v>
+      </c>
+      <c r="E468" t="n">
+        <v>188.42</v>
+      </c>
+      <c r="F468" t="n">
+        <v>233.81</v>
+      </c>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:27+00:00</t>
+        </is>
+      </c>
+      <c r="B469" t="n">
+        <v>228.79</v>
+      </c>
+      <c r="C469" t="n">
+        <v>180.16</v>
+      </c>
+      <c r="D469" t="n">
+        <v>191.1</v>
+      </c>
+      <c r="E469" t="n">
+        <v>187.32</v>
+      </c>
+      <c r="F469" t="n">
+        <v>235.14</v>
+      </c>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -13051,7 +13105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B538"/>
+  <dimension ref="A1:B541"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18434,6 +18488,36 @@
       </c>
       <c r="B538" t="n">
         <v>0.26</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>2026-05-30 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B539" t="n">
+        <v>-0.04</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B540" t="n">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B541" t="n">
+        <v>-0.92</v>
       </c>
     </row>
   </sheetData>
@@ -18596,28 +18680,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.01743255974319417</v>
+        <v>-0.0112885618117931</v>
       </c>
       <c r="J2" t="n">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="K2" t="n">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0005899832978841779</v>
+        <v>0.0002479224626029675</v>
       </c>
       <c r="M2" t="n">
-        <v>3.607933354421723</v>
+        <v>3.621553926649974</v>
       </c>
       <c r="N2" t="n">
-        <v>31.37796613776765</v>
+        <v>31.48583080631345</v>
       </c>
       <c r="O2" t="n">
-        <v>5.601603889759401</v>
+        <v>5.611223646078763</v>
       </c>
       <c r="P2" t="n">
-        <v>221.6881812195797</v>
+        <v>221.6267518902112</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18668,28 +18752,28 @@
         <v>0.1105</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4552534037357339</v>
+        <v>-0.4525763093006209</v>
       </c>
       <c r="J3" t="n">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="K3" t="n">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3055115919997312</v>
+        <v>0.3046889185840906</v>
       </c>
       <c r="M3" t="n">
-        <v>3.798806253508947</v>
+        <v>3.796537462627859</v>
       </c>
       <c r="N3" t="n">
-        <v>28.48762973263661</v>
+        <v>28.41156914486547</v>
       </c>
       <c r="O3" t="n">
-        <v>5.337380418579568</v>
+        <v>5.330250382943138</v>
       </c>
       <c r="P3" t="n">
-        <v>189.4545363217463</v>
+        <v>189.4276186024818</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18740,28 +18824,28 @@
         <v>0.08160000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0591007161150534</v>
+        <v>0.06358258376492169</v>
       </c>
       <c r="J4" t="n">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="K4" t="n">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003568941998880915</v>
+        <v>0.004158789710139166</v>
       </c>
       <c r="M4" t="n">
-        <v>6.234769995170586</v>
+        <v>6.225890007832641</v>
       </c>
       <c r="N4" t="n">
-        <v>58.96656876979839</v>
+        <v>58.84215550166099</v>
       </c>
       <c r="O4" t="n">
-        <v>7.678969251781022</v>
+        <v>7.670864064866551</v>
       </c>
       <c r="P4" t="n">
-        <v>184.4024480061476</v>
+        <v>184.357382878415</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18812,28 +18896,28 @@
         <v>0.0892</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1543098395456054</v>
+        <v>-0.1473941905186183</v>
       </c>
       <c r="J5" t="n">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="K5" t="n">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01163442956664573</v>
+        <v>0.0107000019473823</v>
       </c>
       <c r="M5" t="n">
-        <v>9.04391541394844</v>
+        <v>9.037682589802833</v>
       </c>
       <c r="N5" t="n">
-        <v>122.312926693738</v>
+        <v>122.093903709197</v>
       </c>
       <c r="O5" t="n">
-        <v>11.05951747110777</v>
+        <v>11.0496110207191</v>
       </c>
       <c r="P5" t="n">
-        <v>183.5389442057125</v>
+        <v>183.4694072098731</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -18884,28 +18968,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1274388683340576</v>
+        <v>-0.130365756104742</v>
       </c>
       <c r="J6" t="n">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="K6" t="n">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02784266432156968</v>
+        <v>0.02932227731408033</v>
       </c>
       <c r="M6" t="n">
-        <v>4.588064880896566</v>
+        <v>4.584932032435193</v>
       </c>
       <c r="N6" t="n">
-        <v>34.28800237132437</v>
+        <v>34.19743376046522</v>
       </c>
       <c r="O6" t="n">
-        <v>5.855595816936511</v>
+        <v>5.847857193918574</v>
       </c>
       <c r="P6" t="n">
-        <v>241.4866667976285</v>
+        <v>241.5160947405063</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -18943,7 +19027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G467"/>
+  <dimension ref="A1:G469"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36205,6 +36289,80 @@
         </is>
       </c>
     </row>
+    <row r="468">
+      <c r="A468" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-30 22:26:38+00:00</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>-46.889785731308024,168.13907332518437</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>-46.8889606917843,168.13885957452845</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>-46.88889121665424,168.13777389232862</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>-46.88907895308895,168.13676096501533</t>
+        </is>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>-46.88968488525878,168.13594166178055</t>
+        </is>
+      </c>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:27+00:00</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>-46.889785731308024,168.13907332518437</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>-46.8889567418202,168.13886619940038</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>-46.888884621996404,168.13777084572442</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>-46.88906953211677,168.13675661289216</t>
+        </is>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>-46.88969627266166,168.1359469395926</t>
+        </is>
+      </c>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
